--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="87">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -79,6 +82,36 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -115,37 +148,115 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>22:16</t>
-  </si>
-  <si>
-    <t>14:03</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>11:43</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>00:37</t>
-  </si>
-  <si>
-    <t>08:16</t>
-  </si>
-  <si>
-    <t>21:54</t>
-  </si>
-  <si>
-    <t>16:12</t>
-  </si>
-  <si>
-    <t>20:01</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>22:15:00</t>
+  </si>
+  <si>
+    <t>14:03:00</t>
+  </si>
+  <si>
+    <t>18:04:00</t>
+  </si>
+  <si>
+    <t>11:44:00</t>
+  </si>
+  <si>
+    <t>14:57:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>00:36:00</t>
+  </si>
+  <si>
+    <t>08:16:00</t>
+  </si>
+  <si>
+    <t>21:54:00</t>
+  </si>
+  <si>
+    <t>16:12:00</t>
+  </si>
+  <si>
+    <t>20:01:00</t>
+  </si>
+  <si>
+    <t>13:10:00</t>
+  </si>
+  <si>
+    <t>20:06:00</t>
+  </si>
+  <si>
+    <t>08:01:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>21:04:00</t>
+  </si>
+  <si>
+    <t>19:11:00</t>
+  </si>
+  <si>
+    <t>09:54:00</t>
+  </si>
+  <si>
+    <t>3231300072 3231300072</t>
+  </si>
+  <si>
+    <t>3231379343 3231379343</t>
+  </si>
+  <si>
+    <t>3231421951 3231421951</t>
+  </si>
+  <si>
+    <t>3231550706 3231550706</t>
+  </si>
+  <si>
+    <t>3231510294 3231510294</t>
+  </si>
+  <si>
+    <t>3231542529 3231542529</t>
+  </si>
+  <si>
+    <t>3231679750 3231679750</t>
+  </si>
+  <si>
+    <t>3231727737 3231727737</t>
+  </si>
+  <si>
+    <t>3231874180 3231874180</t>
+  </si>
+  <si>
+    <t>3231877961 3231877961</t>
+  </si>
+  <si>
+    <t>3231930117 3231930117</t>
+  </si>
+  <si>
+    <t>3232052132 3232052132</t>
+  </si>
+  <si>
+    <t>3232162563 3232162563</t>
+  </si>
+  <si>
+    <t>3232185391 3232185391</t>
+  </si>
+  <si>
+    <t>3232299764 3232299764</t>
+  </si>
+  <si>
+    <t>3232388065 3232388065</t>
+  </si>
+  <si>
+    <t>3232485298 3232485298</t>
+  </si>
+  <si>
+    <t>3232668308 3232668308</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИЯНИС ВАРНА ООД</t>
@@ -569,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -578,16 +689,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -627,549 +739,893 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1911</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>31.11</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>51.64</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>56</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>172781</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1148</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>42.17</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>70</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>75.91</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>202027</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1147</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <v>25.5</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4">
         <v>1.43</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>36.46</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.52</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>38.76</v>
       </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>47</v>
       </c>
       <c r="M4">
-        <v>102353</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1148</v>
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>42.73</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5">
         <v>1.66</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>70.93000000000001</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>76.91</v>
       </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>48</v>
       </c>
       <c r="M5">
-        <v>203075</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1911</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F6">
         <v>33.27</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6">
         <v>1.66</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>55.23</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.8</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>59.89</v>
       </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>49</v>
       </c>
       <c r="M6">
-        <v>175676</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>1911</v>
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>19.17</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7">
         <v>1.43</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>27.41</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.53</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>29.33</v>
       </c>
-      <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>50</v>
       </c>
       <c r="M7">
-        <v>175680</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>1147</v>
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>29.6</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8">
         <v>1.46</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>43.22</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.54</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>45.58</v>
       </c>
-      <c r="K8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>51</v>
       </c>
       <c r="M8">
-        <v>179004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>1148</v>
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>44.87</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9">
         <v>1.65</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>74.04000000000001</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.79</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>80.31999999999999</v>
       </c>
-      <c r="K9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>52</v>
       </c>
       <c r="M9">
-        <v>204431</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>1147</v>
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F10">
         <v>25.92</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10">
         <v>1.47</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>38.1</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.54</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>39.92</v>
       </c>
-      <c r="K10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>53</v>
       </c>
       <c r="M10">
-        <v>181395</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11">
-        <v>1148</v>
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F11">
         <v>31.65</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11">
         <v>1.65</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>52.22</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.77</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>56.02</v>
       </c>
-      <c r="K11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>54</v>
       </c>
       <c r="M11">
-        <v>206024</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12">
-        <v>1147</v>
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F12">
         <v>49.74</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12">
         <v>1.48</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>73.62</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.54</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>76.59999999999999</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
         <v>43</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>181858</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
+      <c r="F13">
+        <v>26.62</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13">
+        <v>1.48</v>
+      </c>
+      <c r="I13" s="1">
+        <v>39.4</v>
+      </c>
+      <c r="J13">
+        <v>1.55</v>
+      </c>
+      <c r="K13" s="1">
+        <v>41.26</v>
+      </c>
+      <c r="L13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14">
+        <v>35.03</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14">
+        <v>1.63</v>
+      </c>
+      <c r="I14" s="1">
+        <v>57.1</v>
+      </c>
+      <c r="J14">
+        <v>1.75</v>
+      </c>
+      <c r="K14" s="1">
+        <v>61.3</v>
+      </c>
+      <c r="L14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15">
+        <v>51.27</v>
+      </c>
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15">
+        <v>1.63</v>
+      </c>
+      <c r="I15" s="1">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="J15">
+        <v>1.75</v>
+      </c>
+      <c r="K15" s="1">
+        <v>89.72</v>
+      </c>
+      <c r="L15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16">
+        <v>44.81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16">
+        <v>1.63</v>
+      </c>
+      <c r="I16" s="1">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="J16">
+        <v>1.73</v>
+      </c>
+      <c r="K16" s="1">
+        <v>77.52</v>
+      </c>
+      <c r="L16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="6">
-        <v>225.8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>6</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.6566</v>
-      </c>
-      <c r="E17" s="6">
-        <v>374.06</v>
-      </c>
-      <c r="F17" s="6">
-        <v>405.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="6">
-        <v>149.93</v>
-      </c>
-      <c r="C18" s="6">
-        <v>5</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.4594</v>
-      </c>
-      <c r="E18" s="6">
-        <v>218.81</v>
-      </c>
-      <c r="F18" s="6">
-        <v>230.19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="9">
-        <v>375.73</v>
-      </c>
-      <c r="C19" s="9">
-        <v>11</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="9">
-        <v>592.87</v>
-      </c>
-      <c r="F19" s="9">
-        <v>635.24</v>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17">
+        <v>28.06</v>
+      </c>
+      <c r="G17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17">
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>42.09</v>
+      </c>
+      <c r="J17">
+        <v>1.57</v>
+      </c>
+      <c r="K17" s="1">
+        <v>44.05</v>
+      </c>
+      <c r="L17" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18">
+        <v>39.56</v>
+      </c>
+      <c r="G18" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18">
+        <v>1.63</v>
+      </c>
+      <c r="I18" s="1">
+        <v>64.48</v>
+      </c>
+      <c r="J18">
+        <v>1.72</v>
+      </c>
+      <c r="K18" s="1">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19">
+        <v>51.18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19">
+        <v>1.52</v>
+      </c>
+      <c r="I19" s="1">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="J19">
+        <v>1.57</v>
+      </c>
+      <c r="K19" s="1">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6">
+        <v>396.47</v>
+      </c>
+      <c r="C24" s="6">
+        <v>10</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.6451</v>
+      </c>
+      <c r="E24" s="6">
+        <v>652.25</v>
+      </c>
+      <c r="F24" s="6">
+        <v>701.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6">
+        <v>255.79</v>
+      </c>
+      <c r="C25" s="6">
+        <v>8</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1.4781</v>
+      </c>
+      <c r="E25" s="6">
+        <v>378.09</v>
+      </c>
+      <c r="F25" s="6">
+        <v>395.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="9">
+        <v>652.26</v>
+      </c>
+      <c r="C26" s="9">
+        <v>18</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="9">
+        <v>1030.34</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1097.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
@@ -310,7 +310,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,12 +320,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,17 +369,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="103">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -103,16 +112,22 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В9263РМ</t>
@@ -148,67 +163,148 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-06-01 17:09:36</t>
-  </si>
-  <si>
-    <t>2026-06-04 10:23:34</t>
-  </si>
-  <si>
-    <t>2026-06-05 17:16:19</t>
-  </si>
-  <si>
-    <t>2026-06-07 20:36:19</t>
-  </si>
-  <si>
-    <t>2026-06-08 15:13:20</t>
-  </si>
-  <si>
-    <t>2026-06-09 07:06:24</t>
-  </si>
-  <si>
-    <t>2026-06-09 07:08:13</t>
-  </si>
-  <si>
-    <t>2026-06-10 10:11:18</t>
-  </si>
-  <si>
-    <t>2026-06-10 15:16:50</t>
-  </si>
-  <si>
-    <t>2026-06-11 13:33:32</t>
-  </si>
-  <si>
-    <t>2026-06-12 14:16:56</t>
-  </si>
-  <si>
-    <t>2026-06-16 12:27:48</t>
-  </si>
-  <si>
-    <t>2026-06-16 17:56:06</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:21:11</t>
-  </si>
-  <si>
-    <t>2026-06-18 20:19:54</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:12:09</t>
-  </si>
-  <si>
-    <t>2026-06-20 00:08:44</t>
-  </si>
-  <si>
-    <t>2026-06-21 16:31:34</t>
-  </si>
-  <si>
-    <t>2026-06-23 16:54:42</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:31:42</t>
-  </si>
-  <si>
-    <t>2026-06-25 07:33:34</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>17:09:00</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>17:15:00</t>
+  </si>
+  <si>
+    <t>20:36:00</t>
+  </si>
+  <si>
+    <t>15:12:00</t>
+  </si>
+  <si>
+    <t>07:08:00</t>
+  </si>
+  <si>
+    <t>07:06:00</t>
+  </si>
+  <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>15:16:00</t>
+  </si>
+  <si>
+    <t>13:33:00</t>
+  </si>
+  <si>
+    <t>14:17:00</t>
+  </si>
+  <si>
+    <t>12:28:00</t>
+  </si>
+  <si>
+    <t>17:56:00</t>
+  </si>
+  <si>
+    <t>12:21:00</t>
+  </si>
+  <si>
+    <t>20:20:00</t>
+  </si>
+  <si>
+    <t>00:08:00</t>
+  </si>
+  <si>
+    <t>16:31:00</t>
+  </si>
+  <si>
+    <t>16:54:00</t>
+  </si>
+  <si>
+    <t>15:32:00</t>
+  </si>
+  <si>
+    <t>07:33:00</t>
+  </si>
+  <si>
+    <t>13:29:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>18:09:00</t>
+  </si>
+  <si>
+    <t>3232725354 3232725354</t>
+  </si>
+  <si>
+    <t>3232848631 3232848631</t>
+  </si>
+  <si>
+    <t>3232919257 3232919257</t>
+  </si>
+  <si>
+    <t>3232994554 3232994554</t>
+  </si>
+  <si>
+    <t>3233056356 3233056356</t>
+  </si>
+  <si>
+    <t>3233092792 3233092792</t>
+  </si>
+  <si>
+    <t>3233095841 3233095841</t>
+  </si>
+  <si>
+    <t>3233140904 3233140904</t>
+  </si>
+  <si>
+    <t>3233146405 3233146405</t>
+  </si>
+  <si>
+    <t>3233202829 3233202829</t>
+  </si>
+  <si>
+    <t>3233256109 3233256109</t>
+  </si>
+  <si>
+    <t>3233433254 3233433254</t>
+  </si>
+  <si>
+    <t>3233441796 3233441796</t>
+  </si>
+  <si>
+    <t>3233478724 3233478724</t>
+  </si>
+  <si>
+    <t>3233543392 3233543392</t>
+  </si>
+  <si>
+    <t>3233591334 3233591334</t>
+  </si>
+  <si>
+    <t>3233613164 3233613164</t>
+  </si>
+  <si>
+    <t>3233679663 3233679663</t>
+  </si>
+  <si>
+    <t>3233773171 3233773171</t>
+  </si>
+  <si>
+    <t>3233809418 3233809418</t>
+  </si>
+  <si>
+    <t>3233856921 3233856921</t>
+  </si>
+  <si>
+    <t>3233869765 3233869765</t>
+  </si>
+  <si>
+    <t>3234062374 3234062374</t>
+  </si>
+  <si>
+    <t>3234068420 3234068420</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИЯНИС ВАРНА ООД</t>
@@ -626,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -635,14 +731,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -676,853 +775,1183 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F2">
         <v>40.01</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2">
         <v>1.61</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>64.42</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>67.62</v>
       </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F3">
         <v>27.46</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3">
         <v>1.51</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>41.46</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.57</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>43.11</v>
       </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>18.11</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4">
         <v>1.58</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>28.61</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>30.06</v>
       </c>
-      <c r="K4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>31.17</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5">
         <v>1.5</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>46.76</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.56</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>48.63</v>
       </c>
-      <c r="K5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>42.01</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6">
         <v>1.57</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>65.95999999999999</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.64</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>68.90000000000001</v>
       </c>
-      <c r="K6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7">
+        <v>10.6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7">
+        <v>1.48</v>
+      </c>
+      <c r="I7" s="1">
+        <v>15.69</v>
+      </c>
+      <c r="J7">
+        <v>1.56</v>
+      </c>
+      <c r="K7" s="1">
+        <v>16.54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>41</v>
       </c>
-      <c r="F7">
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8">
         <v>10.04</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8">
         <v>1.55</v>
       </c>
-      <c r="H7">
+      <c r="I8" s="1">
         <v>15.56</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J8">
         <v>1.64</v>
       </c>
-      <c r="J7">
+      <c r="K8" s="1">
         <v>16.47</v>
       </c>
-      <c r="K7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8">
-        <v>10.6</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H8">
-        <v>15.69</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J8">
-        <v>16.54</v>
-      </c>
-      <c r="K8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>55.21</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9">
         <v>1.55</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>85.58</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.63</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>89.98999999999999</v>
       </c>
-      <c r="K9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>38.64</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10">
         <v>1.48</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>57.19</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.56</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>60.28</v>
       </c>
-      <c r="K10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F11">
         <v>19.45</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11">
         <v>1.48</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>28.79</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.56</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>30.34</v>
       </c>
-      <c r="K11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F12">
         <v>28.16</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12">
         <v>1.48</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>41.68</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.56</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>43.93</v>
       </c>
-      <c r="K12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F13">
         <v>11.04</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13">
         <v>1.48</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>16.34</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.56</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>17.22</v>
       </c>
-      <c r="K13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>26.92</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14">
         <v>1.48</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>39.84</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.56</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>42</v>
       </c>
-      <c r="K14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F15">
         <v>10.5</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15">
         <v>1.81</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>19</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.81</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>19</v>
       </c>
-      <c r="K15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F16">
         <v>13.62</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16">
         <v>1.81</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>24.65</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.81</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>24.65</v>
       </c>
-      <c r="K16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F17">
         <v>30</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17">
         <v>1.54</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>46.2</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.56</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>46.8</v>
       </c>
-      <c r="K17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F18">
         <v>14.22</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18">
         <v>1.79</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>25.45</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.79</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>25.45</v>
       </c>
-      <c r="K18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F19">
         <v>27.93</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19">
         <v>1.44</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>40.22</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.53</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>42.73</v>
       </c>
-      <c r="K19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F20">
         <v>12.96</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20">
         <v>1.77</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="1">
         <v>22.94</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20">
         <v>1.77</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>22.94</v>
       </c>
-      <c r="K20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F21">
         <v>15.1</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21">
         <v>1.42</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>21.44</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>1.51</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>22.8</v>
       </c>
-      <c r="K21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F22">
         <v>15.55</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22">
         <v>1.77</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="1">
         <v>27.52</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>1.77</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>27.52</v>
       </c>
-      <c r="K22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="L22" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23">
+        <v>26.85</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23">
+        <v>1.41</v>
+      </c>
+      <c r="I23" s="1">
+        <v>37.86</v>
+      </c>
+      <c r="J23">
+        <v>1.5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>40.28</v>
+      </c>
+      <c r="L23" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24">
+        <v>27.39</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24">
+        <v>1.4</v>
+      </c>
+      <c r="I24" s="1">
+        <v>38.35</v>
+      </c>
+      <c r="J24">
+        <v>1.5</v>
+      </c>
+      <c r="K24" s="1">
+        <v>41.08</v>
+      </c>
+      <c r="L24" t="s">
+        <v>71</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25">
+        <v>41.36</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25">
+        <v>1.44</v>
+      </c>
+      <c r="I25" s="1">
+        <v>59.56</v>
+      </c>
+      <c r="J25">
+        <v>1.51</v>
+      </c>
+      <c r="K25" s="1">
+        <v>62.45</v>
+      </c>
+      <c r="L25" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="6">
+        <v>290.71</v>
+      </c>
+      <c r="C30" s="6">
+        <v>12</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.4641</v>
+      </c>
+      <c r="E30" s="6">
+        <v>425.62</v>
+      </c>
+      <c r="F30" s="6">
+        <v>448.94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="6">
+        <v>236.74</v>
+      </c>
+      <c r="C31" s="6">
         <v>7</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="6">
-        <v>236.47</v>
-      </c>
-      <c r="C27" s="6">
-        <v>10</v>
-      </c>
-      <c r="D27" s="7">
-        <v>1.4776</v>
-      </c>
-      <c r="E27" s="6">
-        <v>349.41</v>
-      </c>
-      <c r="F27" s="6">
-        <v>367.58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="6">
-        <v>195.38</v>
-      </c>
-      <c r="C28" s="6">
-        <v>6</v>
-      </c>
-      <c r="D28" s="7">
-        <v>1.5679</v>
-      </c>
-      <c r="E28" s="6">
-        <v>306.33</v>
-      </c>
-      <c r="F28" s="6">
-        <v>319.84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="6">
+      <c r="D31" s="7">
+        <v>1.5455</v>
+      </c>
+      <c r="E31" s="6">
+        <v>365.89</v>
+      </c>
+      <c r="F31" s="6">
+        <v>382.29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="6">
         <v>66.84999999999999</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C32" s="6">
         <v>5</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D32" s="7">
         <v>1.7885</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E32" s="6">
         <v>119.56</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F32" s="6">
         <v>119.56</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="9">
-        <v>498.7</v>
-      </c>
-      <c r="C30" s="9">
-        <v>21</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="9">
-        <v>775.3</v>
-      </c>
-      <c r="F30" s="9">
-        <v>806.98</v>
+    <row r="33" spans="1:6">
+      <c r="A33" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="9">
+        <v>594.3</v>
+      </c>
+      <c r="C33" s="9">
+        <v>24</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="9">
+        <v>911.0700000000001</v>
+      </c>
+      <c r="F33" s="9">
+        <v>950.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="86">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -70,39 +76,72 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1197 Разград</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>В9263РМ</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>В9263РМ</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>78970152027720045</t>
   </si>
   <si>
+    <t>78970152027720029</t>
+  </si>
+  <si>
     <t>78970152027720060</t>
   </si>
   <si>
-    <t>78970152027720029</t>
-  </si>
-  <si>
     <t>78970152027720052</t>
   </si>
   <si>
@@ -112,25 +151,109 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-02 22:35:22</t>
-  </si>
-  <si>
-    <t>2026-07-03 09:38:24</t>
-  </si>
-  <si>
-    <t>2026-07-03 19:41:30</t>
-  </si>
-  <si>
-    <t>2026-07-09 18:02:32</t>
-  </si>
-  <si>
-    <t>2026-07-11 21:24:28</t>
-  </si>
-  <si>
-    <t>2026-07-13 12:13:53</t>
-  </si>
-  <si>
-    <t>2026-07-15 18:35:55</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>22:35:00</t>
+  </si>
+  <si>
+    <t>19:41:00</t>
+  </si>
+  <si>
+    <t>09:37:00</t>
+  </si>
+  <si>
+    <t>18:02:00</t>
+  </si>
+  <si>
+    <t>21:24:00</t>
+  </si>
+  <si>
+    <t>12:13:00</t>
+  </si>
+  <si>
+    <t>18:35:00</t>
+  </si>
+  <si>
+    <t>11:28:00</t>
+  </si>
+  <si>
+    <t>17:01:00</t>
+  </si>
+  <si>
+    <t>18:50:00</t>
+  </si>
+  <si>
+    <t>13:12:00</t>
+  </si>
+  <si>
+    <t>17:09:00</t>
+  </si>
+  <si>
+    <t>16:03:00</t>
+  </si>
+  <si>
+    <t>20:22:00</t>
+  </si>
+  <si>
+    <t>13:27:00</t>
+  </si>
+  <si>
+    <t>:  :00</t>
+  </si>
+  <si>
+    <t>21:13:00</t>
+  </si>
+  <si>
+    <t>3234215380 3234215380</t>
+  </si>
+  <si>
+    <t>3234267693 3234267693</t>
+  </si>
+  <si>
+    <t>3234251247 3234251247</t>
+  </si>
+  <si>
+    <t>3234547823 3234547823</t>
+  </si>
+  <si>
+    <t>3234658030 3234658030</t>
+  </si>
+  <si>
+    <t>3234747216 3234747216</t>
+  </si>
+  <si>
+    <t>3234851116 3234851116</t>
+  </si>
+  <si>
+    <t>3235006634 3235006634</t>
+  </si>
+  <si>
+    <t>3235023693 3235023693</t>
+  </si>
+  <si>
+    <t>3235149404 3235149404</t>
+  </si>
+  <si>
+    <t>3235220177 3235220177</t>
+  </si>
+  <si>
+    <t>3235249446 3235249446</t>
+  </si>
+  <si>
+    <t>3235357564 3235357564</t>
+  </si>
+  <si>
+    <t>3235447636 3235447636</t>
+  </si>
+  <si>
+    <t>3235538415 3235538415</t>
+  </si>
+  <si>
+    <t>3235606284 3235606284</t>
+  </si>
+  <si>
+    <t>3235659304 3235659304</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИЯНИС ВАРНА ООД</t>
@@ -548,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -557,15 +680,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -602,364 +727,849 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>52.14</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2">
         <v>1.4</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>73</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>78.20999999999999</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3">
+        <v>11.34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3">
+        <v>1.4</v>
+      </c>
+      <c r="I3" s="1">
+        <v>15.88</v>
+      </c>
+      <c r="J3">
+        <v>1.5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>17.01</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <v>33.74</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4">
+        <v>1.44</v>
+      </c>
+      <c r="I4" s="1">
+        <v>48.59</v>
+      </c>
+      <c r="J4">
+        <v>1.51</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50.95</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3">
-        <v>33.74</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H3">
-        <v>48.59</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J3">
-        <v>50.95</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>11.34</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="H4">
-        <v>15.88</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J4">
-        <v>17.01</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F5">
         <v>11.23</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5">
         <v>1.4</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>15.72</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.49</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>16.73</v>
       </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>13.28</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6">
         <v>1.4</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>18.59</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.49</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>19.79</v>
       </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>27.8</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7">
         <v>1.4</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>38.92</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.49</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>41.42</v>
       </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8">
         <v>1.41</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>70.5</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.49</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>74.5</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="3" t="s">
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9">
+        <v>52.73</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9">
+        <v>1.57</v>
+      </c>
+      <c r="I9" s="1">
+        <v>82.79000000000001</v>
+      </c>
+      <c r="J9">
+        <v>1.65</v>
+      </c>
+      <c r="K9" s="1">
+        <v>87</v>
+      </c>
+      <c r="L9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10">
+        <v>58.63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10">
+        <v>1.57</v>
+      </c>
+      <c r="I10" s="1">
+        <v>92.05</v>
+      </c>
+      <c r="J10">
+        <v>1.68</v>
+      </c>
+      <c r="K10" s="1">
+        <v>98.5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11">
+        <v>29.37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11">
+        <v>1.43</v>
+      </c>
+      <c r="I11" s="1">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>1.53</v>
+      </c>
+      <c r="K11" s="1">
+        <v>44.94</v>
+      </c>
+      <c r="L11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12">
+        <v>45.27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12">
+        <v>1.62</v>
+      </c>
+      <c r="I12" s="1">
+        <v>73.34</v>
+      </c>
+      <c r="J12">
+        <v>1.7</v>
+      </c>
+      <c r="K12" s="1">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13">
+        <v>47.16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13">
+        <v>1.62</v>
+      </c>
+      <c r="I13" s="1">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="J13">
+        <v>1.7</v>
+      </c>
+      <c r="K13" s="1">
+        <v>80.17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14">
+        <v>34.39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14">
+        <v>1.65</v>
+      </c>
+      <c r="I14" s="1">
+        <v>56.74</v>
+      </c>
+      <c r="J14">
+        <v>1.74</v>
+      </c>
+      <c r="K14" s="1">
+        <v>59.84</v>
+      </c>
+      <c r="L14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15">
+        <v>26.97</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15">
+        <v>1.44</v>
+      </c>
+      <c r="I15" s="1">
+        <v>38.84</v>
+      </c>
+      <c r="J15">
+        <v>1.56</v>
+      </c>
+      <c r="K15" s="1">
+        <v>42.07</v>
+      </c>
+      <c r="L15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16">
+        <v>58.86</v>
+      </c>
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16">
+        <v>1.7</v>
+      </c>
+      <c r="I16" s="1">
+        <v>100.06</v>
+      </c>
+      <c r="J16">
+        <v>1.75</v>
+      </c>
+      <c r="K16" s="1">
+        <v>103</v>
+      </c>
+      <c r="L16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17">
+        <v>28.41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17">
+        <v>1.7</v>
+      </c>
+      <c r="I17" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="J17">
+        <v>1.76</v>
+      </c>
+      <c r="K17" s="1">
+        <v>50</v>
+      </c>
+      <c r="L17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="E18" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="F18">
+        <v>52.56</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18">
+        <v>1.5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>78.84</v>
+      </c>
+      <c r="J18">
+        <v>1.55</v>
+      </c>
+      <c r="K18" s="1">
+        <v>81.47</v>
+      </c>
+      <c r="L18" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="6">
+        <v>359.19</v>
+      </c>
+      <c r="C23" s="6">
+        <v>8</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.6099</v>
+      </c>
+      <c r="E23" s="6">
+        <v>578.27</v>
+      </c>
+      <c r="F23" s="6">
+        <v>606.42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6">
+        <v>274.69</v>
+      </c>
+      <c r="C24" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6">
-        <v>165.79</v>
-      </c>
-      <c r="C13" s="6">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.403</v>
-      </c>
-      <c r="E13" s="6">
-        <v>232.61</v>
-      </c>
-      <c r="F13" s="6">
-        <v>247.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="6">
-        <v>33.74</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.4401</v>
-      </c>
-      <c r="E14" s="6">
-        <v>48.59</v>
-      </c>
-      <c r="F14" s="6">
-        <v>50.95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="9">
-        <v>199.53</v>
-      </c>
-      <c r="C15" s="9">
-        <v>7</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="9">
-        <v>281.2</v>
-      </c>
-      <c r="F15" s="9">
-        <v>298.61</v>
+      <c r="D24" s="7">
+        <v>1.4281</v>
+      </c>
+      <c r="E24" s="6">
+        <v>392.29</v>
+      </c>
+      <c r="F24" s="6">
+        <v>416.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="9">
+        <v>633.88</v>
+      </c>
+      <c r="C25" s="9">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="9">
+        <v>970.5599999999999</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1022.56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
@@ -280,7 +280,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1520,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="7">
-        <v>1.6099</v>
+        <v>1.609928</v>
       </c>
       <c r="E23" s="6">
         <v>578.27</v>
@@ -1540,7 +1540,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="7">
-        <v>1.4281</v>
+        <v>1.428119</v>
       </c>
       <c r="E24" s="6">
         <v>392.29</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="87">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -671,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -684,13 +687,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -733,755 +736,809 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>52.14</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I2" s="1">
-        <v>73</v>
+        <v>1.399</v>
       </c>
       <c r="J2">
+        <v>72.94386</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>78.20999999999999</v>
       </c>
-      <c r="L2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3">
         <v>11.34</v>
       </c>
       <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3">
+        <v>1.359</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J3">
+        <v>15.86466</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L3" s="1">
+        <v>17.01</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>45</v>
       </c>
-      <c r="H3">
-        <v>1.4</v>
-      </c>
-      <c r="I3" s="1">
-        <v>15.88</v>
-      </c>
-      <c r="J3">
-        <v>1.5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>17.01</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3">
+      <c r="F4">
+        <v>33.742</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4">
+        <v>1.399</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.439</v>
+      </c>
+      <c r="J4">
+        <v>48.554738</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L4" s="1">
+        <v>50.95042</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="O4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5">
+        <v>11.228</v>
+      </c>
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5">
+        <v>1.359</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J5">
+        <v>15.707972</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L5" s="1">
+        <v>16.72972</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>41</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E6" t="s">
         <v>44</v>
       </c>
-      <c r="F4">
-        <v>33.74</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4">
-        <v>1.44</v>
-      </c>
-      <c r="I4" s="1">
-        <v>48.59</v>
-      </c>
-      <c r="J4">
-        <v>1.51</v>
-      </c>
-      <c r="K4" s="1">
-        <v>50.95</v>
-      </c>
-      <c r="L4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4">
+      <c r="F6">
+        <v>13.282</v>
+      </c>
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6">
+        <v>1.359</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J6">
+        <v>18.581518</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L6" s="1">
+        <v>19.79018</v>
+      </c>
+      <c r="M6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="O6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>27.799</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7">
+        <v>1.359</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J7">
+        <v>38.890801</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L7" s="1">
+        <v>41.42051</v>
+      </c>
+      <c r="M7" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5">
-        <v>11.23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5">
-        <v>1.4</v>
-      </c>
-      <c r="I5" s="1">
-        <v>15.72</v>
-      </c>
-      <c r="J5">
-        <v>1.49</v>
-      </c>
-      <c r="K5" s="1">
-        <v>16.73</v>
-      </c>
-      <c r="L5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6">
-        <v>13.28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6">
-        <v>1.4</v>
-      </c>
-      <c r="I6" s="1">
-        <v>18.59</v>
-      </c>
-      <c r="J6">
-        <v>1.49</v>
-      </c>
-      <c r="K6" s="1">
-        <v>19.79</v>
-      </c>
-      <c r="L6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7">
-        <v>27.8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7">
-        <v>1.4</v>
-      </c>
-      <c r="I7" s="1">
-        <v>38.92</v>
-      </c>
-      <c r="J7">
-        <v>1.49</v>
-      </c>
-      <c r="K7" s="1">
-        <v>41.42</v>
-      </c>
-      <c r="L7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8">
+        <v>1.369</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.409</v>
+      </c>
+      <c r="J8">
+        <v>70.45</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L8" s="1">
+        <v>74.5</v>
+      </c>
+      <c r="M8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
         <v>45</v>
       </c>
-      <c r="H8">
-        <v>1.41</v>
-      </c>
-      <c r="I8" s="1">
-        <v>70.5</v>
-      </c>
-      <c r="J8">
-        <v>1.49</v>
-      </c>
-      <c r="K8" s="1">
-        <v>74.5</v>
-      </c>
-      <c r="L8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8">
+      <c r="F9">
+        <v>52.727</v>
+      </c>
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9">
+        <v>1.528</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.568</v>
+      </c>
+      <c r="J9">
+        <v>82.67593599999999</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="L9" s="1">
+        <v>86.99955</v>
+      </c>
+      <c r="M9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="O9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>58.631</v>
+      </c>
+      <c r="G10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10">
+        <v>1.528</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.568</v>
+      </c>
+      <c r="J10">
+        <v>91.933408</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L10" s="1">
+        <v>98.50008</v>
+      </c>
+      <c r="M10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11">
+        <v>29.373</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11">
+        <v>1.389</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="J11">
+        <v>41.974017</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="L11" s="1">
+        <v>44.94069</v>
+      </c>
+      <c r="M11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>45.271</v>
+      </c>
+      <c r="G12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12">
+        <v>1.588</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.618</v>
+      </c>
+      <c r="J12">
+        <v>73.24847800000001</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L12" s="1">
+        <v>76.9607</v>
+      </c>
+      <c r="M12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>47.159</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13">
+        <v>1.588</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.618</v>
+      </c>
+      <c r="J13">
+        <v>76.303262</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>80.1703</v>
+      </c>
+      <c r="M13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>38</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>34.391</v>
+      </c>
+      <c r="G14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14">
+        <v>1.619</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J14">
+        <v>56.710759</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L14" s="1">
+        <v>59.84034</v>
+      </c>
+      <c r="M14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
         <v>44</v>
       </c>
-      <c r="F9">
-        <v>52.73</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F15">
+        <v>26.968</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15">
+        <v>1.401</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.441</v>
+      </c>
+      <c r="J15">
+        <v>38.860888</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L15" s="1">
+        <v>42.07008</v>
+      </c>
+      <c r="M15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="H9">
-        <v>1.57</v>
-      </c>
-      <c r="I9" s="1">
-        <v>82.79000000000001</v>
-      </c>
-      <c r="J9">
-        <v>1.65</v>
-      </c>
-      <c r="K9" s="1">
-        <v>87</v>
-      </c>
-      <c r="L9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9">
+      <c r="F16">
+        <v>58.863</v>
+      </c>
+      <c r="G16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16">
+        <v>1.674</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="J16">
+        <v>100.302552</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L16" s="1">
+        <v>103.01025</v>
+      </c>
+      <c r="M16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="O16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17">
+        <v>28.409</v>
+      </c>
+      <c r="G17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17">
+        <v>1.674</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="J17">
+        <v>48.408936</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L17" s="1">
+        <v>49.99984</v>
+      </c>
+      <c r="M17" t="s">
+        <v>62</v>
+      </c>
+      <c r="O17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
         <v>44</v>
       </c>
-      <c r="F10">
-        <v>58.63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10">
-        <v>1.57</v>
-      </c>
-      <c r="I10" s="1">
-        <v>92.05</v>
-      </c>
-      <c r="J10">
-        <v>1.68</v>
-      </c>
-      <c r="K10" s="1">
-        <v>98.5</v>
-      </c>
-      <c r="L10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10">
+      <c r="F18">
+        <v>52.561</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18">
+        <v>1.459</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1.499</v>
+      </c>
+      <c r="J18">
+        <v>78.788939</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L18" s="1">
+        <v>81.46955</v>
+      </c>
+      <c r="M18" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11">
-        <v>29.37</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11">
-        <v>1.43</v>
-      </c>
-      <c r="I11" s="1">
-        <v>42</v>
-      </c>
-      <c r="J11">
-        <v>1.53</v>
-      </c>
-      <c r="K11" s="1">
-        <v>44.94</v>
-      </c>
-      <c r="L11" t="s">
-        <v>55</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12">
-        <v>45.27</v>
-      </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12">
-        <v>1.62</v>
-      </c>
-      <c r="I12" s="1">
-        <v>73.34</v>
-      </c>
-      <c r="J12">
-        <v>1.7</v>
-      </c>
-      <c r="K12" s="1">
-        <v>76.95999999999999</v>
-      </c>
-      <c r="L12" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13">
-        <v>47.16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13">
-        <v>1.62</v>
-      </c>
-      <c r="I13" s="1">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="J13">
-        <v>1.7</v>
-      </c>
-      <c r="K13" s="1">
-        <v>80.17</v>
-      </c>
-      <c r="L13" t="s">
-        <v>57</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14">
-        <v>34.39</v>
-      </c>
-      <c r="G14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14">
-        <v>1.65</v>
-      </c>
-      <c r="I14" s="1">
-        <v>56.74</v>
-      </c>
-      <c r="J14">
-        <v>1.74</v>
-      </c>
-      <c r="K14" s="1">
-        <v>59.84</v>
-      </c>
-      <c r="L14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15">
-        <v>26.97</v>
-      </c>
-      <c r="G15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15">
-        <v>1.44</v>
-      </c>
-      <c r="I15" s="1">
-        <v>38.84</v>
-      </c>
-      <c r="J15">
-        <v>1.56</v>
-      </c>
-      <c r="K15" s="1">
-        <v>42.07</v>
-      </c>
-      <c r="L15" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16">
-        <v>58.86</v>
-      </c>
-      <c r="G16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16">
-        <v>1.7</v>
-      </c>
-      <c r="I16" s="1">
-        <v>100.06</v>
-      </c>
-      <c r="J16">
-        <v>1.75</v>
-      </c>
-      <c r="K16" s="1">
-        <v>103</v>
-      </c>
-      <c r="L16" t="s">
-        <v>60</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17">
-        <v>28.41</v>
-      </c>
-      <c r="G17" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17">
-        <v>1.7</v>
-      </c>
-      <c r="I17" s="1">
-        <v>48.3</v>
-      </c>
-      <c r="J17">
-        <v>1.76</v>
-      </c>
-      <c r="K17" s="1">
-        <v>50</v>
-      </c>
-      <c r="L17" t="s">
-        <v>61</v>
-      </c>
-      <c r="N17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18">
-        <v>52.56</v>
-      </c>
-      <c r="G18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18">
-        <v>1.5</v>
-      </c>
-      <c r="I18" s="1">
-        <v>78.84</v>
-      </c>
-      <c r="J18">
-        <v>1.55</v>
-      </c>
-      <c r="K18" s="1">
-        <v>81.47</v>
-      </c>
-      <c r="L18" t="s">
-        <v>62</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1489,82 +1546,82 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:15">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="6">
-        <v>359.19</v>
+        <v>359.193</v>
       </c>
       <c r="C23" s="6">
         <v>8</v>
       </c>
       <c r="D23" s="7">
-        <v>1.609928</v>
+        <v>1.609547</v>
       </c>
       <c r="E23" s="6">
-        <v>578.27</v>
+        <v>578.14</v>
       </c>
       <c r="F23" s="6">
-        <v>606.42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>606.4299999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6">
-        <v>274.69</v>
+        <v>274.691</v>
       </c>
       <c r="C24" s="6">
         <v>9</v>
       </c>
       <c r="D24" s="7">
-        <v>1.428119</v>
+        <v>1.427286</v>
       </c>
       <c r="E24" s="6">
-        <v>392.29</v>
+        <v>392.06</v>
       </c>
       <c r="F24" s="6">
         <v>416.14</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B25" s="9">
-        <v>633.88</v>
+        <v>633.884</v>
       </c>
       <c r="C25" s="9">
         <v>17</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="9">
-        <v>970.5599999999999</v>
+        <v>970.2</v>
       </c>
       <c r="F25" s="9">
-        <v>1022.56</v>
+        <v>1022.57</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЯНИС ВАРНА ООД/ДИЯНИС ВАРНА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="86">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -282,8 +279,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -376,10 +373,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -674,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -687,13 +684,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -736,809 +733,755 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>52.14</v>
       </c>
       <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>72.944</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="L2" t="s">
         <v>46</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.399</v>
-      </c>
-      <c r="J2">
-        <v>72.94386</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>78.20999999999999</v>
-      </c>
-      <c r="M2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3">
         <v>11.34</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>15.865</v>
       </c>
       <c r="J3">
-        <v>15.86466</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
         <v>17.01</v>
       </c>
-      <c r="M3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4">
         <v>33.742</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4">
-        <v>1.399</v>
+        <v>1.439</v>
       </c>
       <c r="I4" s="1">
-        <v>1.439</v>
+        <v>48.555</v>
       </c>
       <c r="J4">
-        <v>48.554738</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
-        <v>50.95042</v>
-      </c>
-      <c r="M4" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>50.95</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5">
         <v>11.228</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I5" s="1">
-        <v>1.399</v>
+        <v>15.708</v>
       </c>
       <c r="J5">
-        <v>15.707972</v>
+        <v>1.49</v>
       </c>
       <c r="K5" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L5" s="1">
-        <v>16.72972</v>
-      </c>
-      <c r="M5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>16.73</v>
+      </c>
+      <c r="L5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>13.282</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I6" s="1">
-        <v>1.399</v>
+        <v>18.582</v>
       </c>
       <c r="J6">
-        <v>18.581518</v>
+        <v>1.49</v>
       </c>
       <c r="K6" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L6" s="1">
-        <v>19.79018</v>
-      </c>
-      <c r="M6" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>19.79</v>
+      </c>
+      <c r="L6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
         <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
       </c>
       <c r="F7">
         <v>27.799</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I7" s="1">
-        <v>1.399</v>
+        <v>38.891</v>
       </c>
       <c r="J7">
-        <v>38.890801</v>
+        <v>1.49</v>
       </c>
       <c r="K7" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L7" s="1">
-        <v>41.42051</v>
-      </c>
-      <c r="M7" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>41.421</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8">
-        <v>1.369</v>
+        <v>1.409</v>
       </c>
       <c r="I8" s="1">
-        <v>1.409</v>
+        <v>70.45</v>
       </c>
       <c r="J8">
-        <v>70.45</v>
+        <v>1.49</v>
       </c>
       <c r="K8" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L8" s="1">
         <v>74.5</v>
       </c>
-      <c r="M8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="L8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>52.727</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9">
-        <v>1.528</v>
+        <v>1.568</v>
       </c>
       <c r="I9" s="1">
-        <v>1.568</v>
+        <v>82.676</v>
       </c>
       <c r="J9">
-        <v>82.67593599999999</v>
+        <v>1.65</v>
       </c>
       <c r="K9" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="L9" s="1">
-        <v>86.99955</v>
-      </c>
-      <c r="M9" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>87</v>
+      </c>
+      <c r="L9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>58.631</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10">
-        <v>1.528</v>
+        <v>1.568</v>
       </c>
       <c r="I10" s="1">
-        <v>1.568</v>
+        <v>91.93300000000001</v>
       </c>
       <c r="J10">
-        <v>91.933408</v>
+        <v>1.68</v>
       </c>
       <c r="K10" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L10" s="1">
-        <v>98.50008</v>
-      </c>
-      <c r="M10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>98.5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
       </c>
       <c r="F11">
         <v>29.373</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11">
-        <v>1.389</v>
+        <v>1.429</v>
       </c>
       <c r="I11" s="1">
-        <v>1.429</v>
+        <v>41.974</v>
       </c>
       <c r="J11">
-        <v>41.974017</v>
+        <v>1.53</v>
       </c>
       <c r="K11" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L11" s="1">
-        <v>44.94069</v>
-      </c>
-      <c r="M11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>44.941</v>
+      </c>
+      <c r="L11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12">
         <v>45.271</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I12" s="1">
-        <v>1.618</v>
+        <v>73.248</v>
       </c>
       <c r="J12">
-        <v>73.24847800000001</v>
+        <v>1.7</v>
       </c>
       <c r="K12" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L12" s="1">
-        <v>76.9607</v>
-      </c>
-      <c r="M12" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>76.961</v>
+      </c>
+      <c r="L12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13">
         <v>47.159</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H13">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I13" s="1">
-        <v>1.618</v>
+        <v>76.303</v>
       </c>
       <c r="J13">
-        <v>76.303262</v>
+        <v>1.7</v>
       </c>
       <c r="K13" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L13" s="1">
-        <v>80.1703</v>
-      </c>
-      <c r="M13" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>80.17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14">
         <v>34.391</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H14">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I14" s="1">
-        <v>1.649</v>
+        <v>56.711</v>
       </c>
       <c r="J14">
-        <v>56.710759</v>
+        <v>1.74</v>
       </c>
       <c r="K14" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L14" s="1">
-        <v>59.84034</v>
-      </c>
-      <c r="M14" t="s">
-        <v>59</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>59.84</v>
+      </c>
+      <c r="L14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
         <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>44</v>
       </c>
       <c r="F15">
         <v>26.968</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I15" s="1">
-        <v>1.441</v>
+        <v>38.861</v>
       </c>
       <c r="J15">
-        <v>38.860888</v>
+        <v>1.56</v>
       </c>
       <c r="K15" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L15" s="1">
-        <v>42.07008</v>
-      </c>
-      <c r="M15" t="s">
-        <v>60</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>42.07</v>
+      </c>
+      <c r="L15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16">
         <v>58.863</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H16">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I16" s="1">
-        <v>1.704</v>
+        <v>100.303</v>
       </c>
       <c r="J16">
-        <v>100.302552</v>
+        <v>1.75</v>
       </c>
       <c r="K16" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L16" s="1">
-        <v>103.01025</v>
-      </c>
-      <c r="M16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>103.01</v>
+      </c>
+      <c r="L16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17">
         <v>28.409</v>
       </c>
       <c r="G17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I17" s="1">
-        <v>1.704</v>
+        <v>48.409</v>
       </c>
       <c r="J17">
-        <v>48.408936</v>
+        <v>1.76</v>
       </c>
       <c r="K17" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L17" s="1">
-        <v>49.99984</v>
-      </c>
-      <c r="M17" t="s">
-        <v>62</v>
-      </c>
-      <c r="O17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>50</v>
+      </c>
+      <c r="L17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18">
         <v>52.561</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H18">
-        <v>1.459</v>
+        <v>1.499</v>
       </c>
       <c r="I18" s="1">
-        <v>1.499</v>
+        <v>78.789</v>
       </c>
       <c r="J18">
-        <v>78.788939</v>
+        <v>1.55</v>
       </c>
       <c r="K18" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L18" s="1">
-        <v>81.46955</v>
-      </c>
-      <c r="M18" t="s">
-        <v>63</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
+        <v>81.47</v>
+      </c>
+      <c r="L18" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="3" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1546,69 +1489,69 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:14">
       <c r="A22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="6">
         <v>359.193</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <v>8</v>
       </c>
       <c r="D23" s="7">
-        <v>1.609547</v>
-      </c>
-      <c r="E23" s="6">
-        <v>578.14</v>
-      </c>
-      <c r="F23" s="6">
-        <v>606.4299999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>1.61</v>
+      </c>
+      <c r="E23" s="7">
+        <v>578.138</v>
+      </c>
+      <c r="F23" s="7">
+        <v>606.431</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6">
         <v>274.691</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>9</v>
       </c>
       <c r="D24" s="7">
-        <v>1.427286</v>
-      </c>
-      <c r="E24" s="6">
-        <v>392.06</v>
-      </c>
-      <c r="F24" s="6">
-        <v>416.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>1.427</v>
+      </c>
+      <c r="E24" s="7">
+        <v>392.064</v>
+      </c>
+      <c r="F24" s="7">
+        <v>416.142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" s="9">
         <v>633.884</v>
@@ -1618,10 +1561,10 @@
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="9">
-        <v>970.2</v>
+        <v>970.202</v>
       </c>
       <c r="F25" s="9">
-        <v>1022.57</v>
+        <v>1022.573</v>
       </c>
     </row>
   </sheetData>
